--- a/public/audit-readiness-checklist.xlsx
+++ b/public/audit-readiness-checklist.xlsx
@@ -1319,7 +1319,7 @@
     <row r="49" ht="46" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Daftar Advisory is a non-attest advisory practice, not a registered statutory auditor. This checklist is a general preparation aid, not accounting or assurance advice, and not a compliance assessment. It does not replace the requirements of the applicable auditing standards. Confirm what your audit requires against the issued standards and your auditor's own request list.</t>
+          <t>Daftar Advisory is a non-attest advisory practice, not a registered statutory auditor. This checklist is a general preparation aid, not accounting, assurance, tax or regulatory advice, and not a compliance assessment. It does not replace the requirements of the applicable auditing standards. Confirm what your audit requires against the issued standards and your auditor's own request list.</t>
         </is>
       </c>
     </row>
